--- a/output/validation/commission_2024_rule_comparison.xlsx
+++ b/output/validation/commission_2024_rule_comparison.xlsx
@@ -614,10 +614,10 @@
         <v>4</v>
       </c>
       <c r="C6">
-        <v>-0.88993</v>
+        <v>-0.87993</v>
       </c>
       <c r="D6">
-        <v>-2.08993</v>
+        <v>-2.049930000000001</v>
       </c>
       <c r="E6">
         <v>-0.87993</v>
@@ -632,10 +632,10 @@
         <v>7</v>
       </c>
       <c r="C7">
-        <v>-0.5299299999999998</v>
+        <v>-0.5199299999999998</v>
       </c>
       <c r="D7">
-        <v>-1.669929999999999</v>
+        <v>-1.59993</v>
       </c>
       <c r="E7">
         <v>-0.5199299999999998</v>
@@ -728,10 +728,10 @@
         <v>4</v>
       </c>
       <c r="C12">
-        <v>0.3499259</v>
+        <v>0.3899259</v>
       </c>
       <c r="D12">
-        <v>0.3499259</v>
+        <v>0.3899259</v>
       </c>
       <c r="E12">
         <v>0.3899259</v>
@@ -880,10 +880,10 @@
         <v>4</v>
       </c>
       <c r="C20">
-        <v>0.8316090000000005</v>
+        <v>0.9116089999999999</v>
       </c>
       <c r="D20">
-        <v>0.8747089999998466</v>
+        <v>0.9116089999999999</v>
       </c>
       <c r="E20">
         <v>0.9116089999999999</v>
@@ -1032,10 +1032,10 @@
         <v>4</v>
       </c>
       <c r="C28">
-        <v>-0.6711990000000001</v>
+        <v>-0.6311990000000001</v>
       </c>
       <c r="D28">
-        <v>-0.6711990000000001</v>
+        <v>-0.6311990000000001</v>
       </c>
       <c r="E28">
         <v>-0.6311990000000001</v>
@@ -1108,10 +1108,10 @@
         <v>4</v>
       </c>
       <c r="C32">
-        <v>-0.1424659999999999</v>
+        <v>-0.1324659999999999</v>
       </c>
       <c r="D32">
-        <v>-1.282466</v>
+        <v>-1.242466</v>
       </c>
       <c r="E32">
         <v>-0.04246599999999989</v>
@@ -1146,10 +1146,10 @@
         <v>4</v>
       </c>
       <c r="C34">
-        <v>0.2302009</v>
+        <v>0.2702009</v>
       </c>
       <c r="D34">
-        <v>0.2302009</v>
+        <v>0.2702009</v>
       </c>
       <c r="E34">
         <v>0.2702009</v>
@@ -1184,10 +1184,10 @@
         <v>4</v>
       </c>
       <c r="C36">
-        <v>-0.2622968999999999</v>
+        <v>-0.2222969</v>
       </c>
       <c r="D36">
-        <v>-0.2622968999999999</v>
+        <v>-0.2222969</v>
       </c>
       <c r="E36">
         <v>-0.2222969</v>
@@ -1202,10 +1202,10 @@
         <v>7</v>
       </c>
       <c r="C37">
-        <v>-0.3222969</v>
+        <v>-0.2522969</v>
       </c>
       <c r="D37">
-        <v>-0.3222969</v>
+        <v>-0.2522969</v>
       </c>
       <c r="E37">
         <v>-0.2522969</v>
@@ -1222,10 +1222,10 @@
         <v>4</v>
       </c>
       <c r="C38">
-        <v>-0.8676448494267694</v>
+        <v>-0.8674228931928216</v>
       </c>
       <c r="D38">
-        <v>-1.137243</v>
+        <v>-1.057243</v>
       </c>
       <c r="E38">
         <v>-0.8674228931928216</v>
@@ -1260,10 +1260,10 @@
         <v>4</v>
       </c>
       <c r="C40">
-        <v>0.03831090000000009</v>
+        <v>0.07831089999999996</v>
       </c>
       <c r="D40">
-        <v>0.03831090000000009</v>
+        <v>0.07831089999999996</v>
       </c>
       <c r="E40">
         <v>0.07831089999999996</v>
@@ -1298,10 +1298,10 @@
         <v>4</v>
       </c>
       <c r="C42">
-        <v>0.7062990000000005</v>
+        <v>0.7462989999999999</v>
       </c>
       <c r="D42">
-        <v>0.7449989999998869</v>
+        <v>0.7462989999999999</v>
       </c>
       <c r="E42">
         <v>0.7462989999999999</v>
@@ -1316,7 +1316,7 @@
         <v>7</v>
       </c>
       <c r="C43">
-        <v>1.181673764103333</v>
+        <v>1.182566437820241</v>
       </c>
       <c r="D43">
         <v>0.9222990000000002</v>
@@ -1374,10 +1374,10 @@
         <v>4</v>
       </c>
       <c r="C46">
-        <v>0.5131050000000004</v>
+        <v>0.5531050000000006</v>
       </c>
       <c r="D46">
-        <v>0.5402049999997562</v>
+        <v>0.5531050000000006</v>
       </c>
       <c r="E46">
         <v>0.5531050000000006</v>
@@ -1392,10 +1392,10 @@
         <v>7</v>
       </c>
       <c r="C47">
-        <v>0.773105000000001</v>
+        <v>0.8431050000000004</v>
       </c>
       <c r="D47">
-        <v>0.7857049999999197</v>
+        <v>0.8431050000000004</v>
       </c>
       <c r="E47">
         <v>1.053105000000001</v>
@@ -1526,10 +1526,10 @@
         <v>4</v>
       </c>
       <c r="C54">
-        <v>-0.7672207999999999</v>
+        <v>-0.7372207999999999</v>
       </c>
       <c r="D54">
-        <v>-1.7872208</v>
+        <v>-1.7472208</v>
       </c>
       <c r="E54">
         <v>-0.7372207999999999</v>
@@ -1544,10 +1544,10 @@
         <v>7</v>
       </c>
       <c r="C55">
-        <v>-0.6572207999999999</v>
+        <v>-1.2172208</v>
       </c>
       <c r="D55">
-        <v>-1.8972208</v>
+        <v>-1.8272208</v>
       </c>
       <c r="E55">
         <v>-1.2172208</v>
